--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3382,6 +3382,108 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122440642</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90754</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brostugugölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>571450</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6506512</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90754</v>
+        <v>90766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90766</v>
+        <v>90773</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90773</v>
+        <v>90778</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,11 +3401,6 @@
       </c>
       <c r="E25" t="n">
         <v>5447</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90778</v>
+        <v>90791</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,6 +3401,11 @@
       </c>
       <c r="E25" t="n">
         <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90791</v>
+        <v>90804</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90804</v>
+        <v>90798</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90798</v>
+        <v>90799</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90799</v>
+        <v>90802</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90802</v>
+        <v>90905</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17417-2021 artfynd.xlsx
+++ b/artfynd/A 17417-2021 artfynd.xlsx
@@ -3387,7 +3387,7 @@
         <v>122440642</v>
       </c>
       <c r="B25" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
